--- a/artfynd/A 26438-2024 artfynd.xlsx
+++ b/artfynd/A 26438-2024 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122476128</v>
+        <v>122476130</v>
       </c>
       <c r="B3" t="n">
         <v>57478</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>432373</v>
+        <v>432271</v>
       </c>
       <c r="R3" t="n">
-        <v>7056594</v>
+        <v>7056616</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122476127</v>
+        <v>122476133</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>432427</v>
+        <v>432125</v>
       </c>
       <c r="R4" t="n">
-        <v>7056564</v>
+        <v>7056413</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122476125</v>
+        <v>122476131</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>432579</v>
+        <v>432150</v>
       </c>
       <c r="R5" t="n">
-        <v>7056500</v>
+        <v>7056415</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122476137</v>
+        <v>122476134</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>432388</v>
+        <v>432164</v>
       </c>
       <c r="R6" t="n">
-        <v>7056290</v>
+        <v>7056388</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122476130</v>
+        <v>122476125</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>432271</v>
+        <v>432579</v>
       </c>
       <c r="R7" t="n">
-        <v>7056616</v>
+        <v>7056500</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122476122</v>
+        <v>122476136</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>432609</v>
+        <v>432216</v>
       </c>
       <c r="R8" t="n">
-        <v>7056392</v>
+        <v>7056375</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122476157</v>
+        <v>122476137</v>
       </c>
       <c r="B9" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,21 +1440,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>432421</v>
+        <v>432388</v>
       </c>
       <c r="R9" t="n">
-        <v>7056565</v>
+        <v>7056290</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>mycket rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122476131</v>
+        <v>122476157</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1547,21 +1547,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>432150</v>
+        <v>432421</v>
       </c>
       <c r="R10" t="n">
-        <v>7056415</v>
+        <v>7056565</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>mycket rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122476133</v>
+        <v>122476127</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>432125</v>
+        <v>432427</v>
       </c>
       <c r="R11" t="n">
-        <v>7056413</v>
+        <v>7056564</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122476136</v>
+        <v>122476128</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>432216</v>
+        <v>432373</v>
       </c>
       <c r="R12" t="n">
-        <v>7056375</v>
+        <v>7056594</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122476134</v>
+        <v>122476122</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>432164</v>
+        <v>432609</v>
       </c>
       <c r="R13" t="n">
-        <v>7056388</v>
+        <v>7056392</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 26438-2024 artfynd.xlsx
+++ b/artfynd/A 26438-2024 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122476130</v>
+        <v>122476134</v>
       </c>
       <c r="B3" t="n">
         <v>57478</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>432271</v>
+        <v>432164</v>
       </c>
       <c r="R3" t="n">
-        <v>7056616</v>
+        <v>7056388</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122476133</v>
+        <v>122476125</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>432125</v>
+        <v>432579</v>
       </c>
       <c r="R4" t="n">
-        <v>7056413</v>
+        <v>7056500</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122476131</v>
+        <v>122476133</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>432150</v>
+        <v>432125</v>
       </c>
       <c r="R5" t="n">
-        <v>7056415</v>
+        <v>7056413</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122476134</v>
+        <v>122476136</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>432164</v>
+        <v>432216</v>
       </c>
       <c r="R6" t="n">
-        <v>7056388</v>
+        <v>7056375</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122476125</v>
+        <v>122476122</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>432579</v>
+        <v>432609</v>
       </c>
       <c r="R7" t="n">
-        <v>7056500</v>
+        <v>7056392</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122476136</v>
+        <v>122476130</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>432216</v>
+        <v>432271</v>
       </c>
       <c r="R8" t="n">
-        <v>7056375</v>
+        <v>7056616</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122476137</v>
+        <v>122476131</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>432388</v>
+        <v>432150</v>
       </c>
       <c r="R9" t="n">
-        <v>7056290</v>
+        <v>7056415</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122476157</v>
+        <v>122476127</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1547,21 +1547,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>432421</v>
+        <v>432427</v>
       </c>
       <c r="R10" t="n">
-        <v>7056565</v>
+        <v>7056564</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>mycket rikligt</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122476127</v>
+        <v>122476137</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>432427</v>
+        <v>432388</v>
       </c>
       <c r="R11" t="n">
-        <v>7056564</v>
+        <v>7056290</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122476128</v>
+        <v>122476157</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1761,21 +1761,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>432373</v>
+        <v>432421</v>
       </c>
       <c r="R12" t="n">
-        <v>7056594</v>
+        <v>7056565</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>mycket rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122476122</v>
+        <v>122476128</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>432609</v>
+        <v>432373</v>
       </c>
       <c r="R13" t="n">
-        <v>7056392</v>
+        <v>7056594</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 26438-2024 artfynd.xlsx
+++ b/artfynd/A 26438-2024 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122476134</v>
+        <v>122476136</v>
       </c>
       <c r="B3" t="n">
         <v>57478</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>432164</v>
+        <v>432216</v>
       </c>
       <c r="R3" t="n">
-        <v>7056388</v>
+        <v>7056375</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122476125</v>
+        <v>122476134</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>432579</v>
+        <v>432164</v>
       </c>
       <c r="R4" t="n">
-        <v>7056500</v>
+        <v>7056388</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122476133</v>
+        <v>122476127</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>432125</v>
+        <v>432427</v>
       </c>
       <c r="R5" t="n">
-        <v>7056413</v>
+        <v>7056564</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122476136</v>
+        <v>122476157</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>432216</v>
+        <v>432421</v>
       </c>
       <c r="R6" t="n">
-        <v>7056375</v>
+        <v>7056565</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>mycket rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122476122</v>
+        <v>122476128</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>432609</v>
+        <v>432373</v>
       </c>
       <c r="R7" t="n">
-        <v>7056392</v>
+        <v>7056594</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122476130</v>
+        <v>122476133</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>432271</v>
+        <v>432125</v>
       </c>
       <c r="R8" t="n">
-        <v>7056616</v>
+        <v>7056413</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122476131</v>
+        <v>122476122</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>432150</v>
+        <v>432609</v>
       </c>
       <c r="R9" t="n">
-        <v>7056415</v>
+        <v>7056392</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122476127</v>
+        <v>122476137</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>432427</v>
+        <v>432388</v>
       </c>
       <c r="R10" t="n">
-        <v>7056564</v>
+        <v>7056290</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122476137</v>
+        <v>122476130</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>432388</v>
+        <v>432271</v>
       </c>
       <c r="R11" t="n">
-        <v>7056290</v>
+        <v>7056616</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122476157</v>
+        <v>122476131</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1761,21 +1761,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>432421</v>
+        <v>432150</v>
       </c>
       <c r="R12" t="n">
-        <v>7056565</v>
+        <v>7056415</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>mycket rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122476128</v>
+        <v>122476125</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>432373</v>
+        <v>432579</v>
       </c>
       <c r="R13" t="n">
-        <v>7056594</v>
+        <v>7056500</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
